--- a/tests/testdata/excel/2025/見積/A社.xlsx
+++ b/tests/testdata/excel/2025/見積/A社.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{089D88A0-A125-44FF-B011-6450E7754C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30A46567-E23A-4D19-ABDD-AF72E4E6CB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{53E33BD4-5683-4ECE-90CF-1674A0403E82}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{CB7B021F-7F00-46C9-AE07-37F29B4B18BE}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -452,7 +452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299B4769-728A-482E-B736-F7C65AF1BE19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19A8D1A-06C7-497F-9589-44EA0245F513}">
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -481,7 +481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7FB65A0-CAC9-4A50-8140-8F20AFE5F7B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEC198C-F6A2-4E3B-BF8B-11BB913CC4C7}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/2025/見積/A社.xlsx
+++ b/tests/testdata/excel/2025/見積/A社.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30A46567-E23A-4D19-ABDD-AF72E4E6CB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3FA6205-B380-474C-B4FC-E737A93E94DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{CB7B021F-7F00-46C9-AE07-37F29B4B18BE}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{47851DE8-286F-44CD-B186-8EDCD9AED08F}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -452,7 +452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F19A8D1A-06C7-497F-9589-44EA0245F513}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BBB2D0-280F-4DB9-A107-9B771430A07A}">
   <dimension ref="B2:C4"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -481,7 +481,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FEC198C-F6A2-4E3B-BF8B-11BB913CC4C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48126834-2892-490D-8404-CF4125F366BC}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
